--- a/03_outputs/01_tables/species_morphology_summary.xlsx
+++ b/03_outputs/01_tables/species_morphology_summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,12 +377,37 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>SD fork length (mm)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Width range (mm)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Mean width (mm)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SD width (mm)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mass range (mm)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Mass (mm)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SD Mass (mm)</t>
         </is>
       </c>
     </row>
@@ -404,10 +429,29 @@
         <v>255.9</v>
       </c>
       <c r="E2">
+        <v>73.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19–80</t>
+        </is>
+      </c>
+      <c r="G2">
         <v>45.1</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>14.3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20–793</t>
+        </is>
+      </c>
+      <c r="J2">
+        <v>307.1</v>
+      </c>
+      <c r="K2">
+        <v>226</v>
       </c>
     </row>
     <row r="3">
@@ -428,10 +472,29 @@
         <v>263.6</v>
       </c>
       <c r="E3">
+        <v>141.8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8–90</t>
+        </is>
+      </c>
+      <c r="G3">
         <v>40</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>27</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10–2480</t>
+        </is>
+      </c>
+      <c r="J3">
+        <v>738.9</v>
+      </c>
+      <c r="K3">
+        <v>849</v>
       </c>
     </row>
     <row r="4">
@@ -452,10 +515,29 @@
         <v>137.9</v>
       </c>
       <c r="E4">
+        <v>44</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7–30</t>
+        </is>
+      </c>
+      <c r="G4">
         <v>18.5</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>6.6</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10–219</t>
+        </is>
+      </c>
+      <c r="J4">
+        <v>46.4</v>
+      </c>
+      <c r="K4">
+        <v>48.8</v>
       </c>
     </row>
     <row r="5">
@@ -476,10 +558,29 @@
         <v>205.9</v>
       </c>
       <c r="E5">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10–95</t>
+        </is>
+      </c>
+      <c r="G5">
         <v>40.3</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>22.2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15–1610</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>361.3</v>
+      </c>
+      <c r="K5">
+        <v>378.2</v>
       </c>
     </row>
     <row r="6">
@@ -500,10 +601,29 @@
         <v>173.7</v>
       </c>
       <c r="E6">
+        <v>21.4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19–34</t>
+        </is>
+      </c>
+      <c r="G6">
         <v>23.8</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>4.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>38–215</t>
+        </is>
+      </c>
+      <c r="J6">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="K6">
+        <v>45.2</v>
       </c>
     </row>
     <row r="7">
@@ -524,10 +644,29 @@
         <v>237.2</v>
       </c>
       <c r="E7">
+        <v>68.8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>15–56</t>
+        </is>
+      </c>
+      <c r="G7">
         <v>33.2</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>11.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18–1201</t>
+        </is>
+      </c>
+      <c r="J7">
+        <v>362.5</v>
+      </c>
+      <c r="K7">
+        <v>338.4</v>
       </c>
     </row>
     <row r="8">
@@ -548,10 +687,29 @@
         <v>287.1</v>
       </c>
       <c r="E8">
+        <v>125.9</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10–64</t>
+        </is>
+      </c>
+      <c r="G8">
         <v>36.5</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>18.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>23–1410</t>
+        </is>
+      </c>
+      <c r="J8">
+        <v>603.8</v>
+      </c>
+      <c r="K8">
+        <v>522.5</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +730,29 @@
         <v>190.2</v>
       </c>
       <c r="E9">
+        <v>42.3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14–40</t>
+        </is>
+      </c>
+      <c r="G9">
         <v>27</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>7.2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15–340</t>
+        </is>
+      </c>
+      <c r="J9">
+        <v>166.2</v>
+      </c>
+      <c r="K9">
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -596,10 +773,29 @@
         <v>578.9</v>
       </c>
       <c r="E10">
+        <v>109.6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>39–100</t>
+        </is>
+      </c>
+      <c r="G10">
         <v>81.40000000000001</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>16.9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>260–4400</t>
+        </is>
+      </c>
+      <c r="J10">
+        <v>2626</v>
+      </c>
+      <c r="K10">
+        <v>954.6</v>
       </c>
     </row>
     <row r="11">
@@ -620,10 +816,29 @@
         <v>468.1</v>
       </c>
       <c r="E11">
+        <v>157.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25–85</t>
+        </is>
+      </c>
+      <c r="G11">
         <v>60.8</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>20.7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>106–3390</t>
+        </is>
+      </c>
+      <c r="J11">
+        <v>1417.6</v>
+      </c>
+      <c r="K11">
+        <v>1117.9</v>
       </c>
     </row>
     <row r="12">
@@ -644,10 +859,29 @@
         <v>365.4</v>
       </c>
       <c r="E12">
+        <v>131.8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30–73</t>
+        </is>
+      </c>
+      <c r="G12">
         <v>50.6</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>16.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>160–1910</t>
+        </is>
+      </c>
+      <c r="J12">
+        <v>881</v>
+      </c>
+      <c r="K12">
+        <v>712.8</v>
       </c>
     </row>
     <row r="13">
@@ -668,10 +902,29 @@
         <v>96</v>
       </c>
       <c r="E13">
+        <v>17.7</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6–22</t>
+        </is>
+      </c>
+      <c r="G13">
         <v>13</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>5.7</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8–20</t>
+        </is>
+      </c>
+      <c r="J13">
+        <v>14.4</v>
+      </c>
+      <c r="K13">
+        <v>4.2</v>
       </c>
     </row>
     <row r="14">
@@ -692,10 +945,29 @@
         <v>429.2</v>
       </c>
       <c r="E14">
+        <v>232.2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15–126</t>
+        </is>
+      </c>
+      <c r="G14">
         <v>74.2</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>45.3</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>23–5110</t>
+        </is>
+      </c>
+      <c r="J14">
+        <v>2640.2</v>
+      </c>
+      <c r="K14">
+        <v>2304.9</v>
       </c>
     </row>
     <row r="15">
@@ -716,10 +988,29 @@
         <v>563</v>
       </c>
       <c r="E15">
+        <v>22.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>83–99</t>
+        </is>
+      </c>
+      <c r="G15">
         <v>90</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>8.199999999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>259–3020</t>
+        </is>
+      </c>
+      <c r="J15">
+        <v>2093</v>
+      </c>
+      <c r="K15">
+        <v>1588.3</v>
       </c>
     </row>
     <row r="16">
@@ -740,10 +1031,29 @@
         <v>465.5</v>
       </c>
       <c r="E16">
+        <v>64.3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>450–650</t>
+        </is>
+      </c>
+      <c r="G16">
         <v>550</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>141.4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>750–1330</t>
+        </is>
+      </c>
+      <c r="J16">
+        <v>1040</v>
+      </c>
+      <c r="K16">
+        <v>410.1</v>
       </c>
     </row>
     <row r="17">
@@ -764,10 +1074,29 @@
         <v>810.5</v>
       </c>
       <c r="E17">
+        <v>120.9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>90–120</t>
+        </is>
+      </c>
+      <c r="G17">
         <v>105</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>21.2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5270–8620</t>
+        </is>
+      </c>
+      <c r="J17">
+        <v>6945</v>
+      </c>
+      <c r="K17">
+        <v>2368.8</v>
       </c>
     </row>
     <row r="18">
@@ -788,10 +1117,29 @@
         <v>97</v>
       </c>
       <c r="E18">
+        <v>4.2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7–10</t>
+        </is>
+      </c>
+      <c r="G18">
         <v>8.5</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>2.1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10–10</t>
+        </is>
+      </c>
+      <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -812,10 +1160,29 @@
         <v>781.5</v>
       </c>
       <c r="E19">
+        <v>228.4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>63–90</t>
+        </is>
+      </c>
+      <c r="G19">
         <v>76.5</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>19.1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1940–5950</t>
+        </is>
+      </c>
+      <c r="J19">
+        <v>3945</v>
+      </c>
+      <c r="K19">
+        <v>2835.5</v>
       </c>
     </row>
     <row r="20">
@@ -836,10 +1203,29 @@
         <v>422.5</v>
       </c>
       <c r="E20">
+        <v>378.3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>22–75</t>
+        </is>
+      </c>
+      <c r="G20">
         <v>48.5</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>37.5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40–3920</t>
+        </is>
+      </c>
+      <c r="J20">
+        <v>1980</v>
+      </c>
+      <c r="K20">
+        <v>2743.6</v>
       </c>
     </row>
     <row r="21">
@@ -859,7 +1245,20 @@
       <c r="D21">
         <v>51</v>
       </c>
-      <c r="E21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4–4</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4–4</t>
+        </is>
+      </c>
+      <c r="J21">
         <v>4</v>
       </c>
     </row>
